--- a/artfynd/A 22458-2024 artfynd.xlsx
+++ b/artfynd/A 22458-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916246</v>
+        <v>118916278</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>79600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862723</v>
+        <v>862932</v>
       </c>
       <c r="R2" t="n">
-        <v>7312315</v>
+        <v>7312260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916279</v>
+        <v>118916256</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,27 +789,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862909</v>
+        <v>862872</v>
       </c>
       <c r="R3" t="n">
-        <v>7312283</v>
+        <v>7312079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916283</v>
+        <v>118916246</v>
       </c>
       <c r="B4" t="n">
-        <v>97766</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,23 +887,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862846</v>
+        <v>862723</v>
       </c>
       <c r="R4" t="n">
-        <v>7312100</v>
+        <v>7312315</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916288</v>
+        <v>118916287</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>97766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1091,27 +1091,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1119,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862878</v>
+        <v>862908</v>
       </c>
       <c r="R6" t="n">
-        <v>7312306</v>
+        <v>7312314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916281</v>
+        <v>118916248</v>
       </c>
       <c r="B7" t="n">
-        <v>79600</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1193,25 +1189,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862909</v>
+        <v>862924</v>
       </c>
       <c r="R7" t="n">
-        <v>7312283</v>
+        <v>7312225</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,10 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118916273</v>
+        <v>118916284</v>
       </c>
       <c r="B8" t="n">
-        <v>97766</v>
+        <v>90504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1295,23 +1291,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862880</v>
+        <v>862907</v>
       </c>
       <c r="R8" t="n">
-        <v>7312302</v>
+        <v>7312315</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,10 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118916244</v>
+        <v>118916273</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
+        <v>97766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,23 +1397,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1421,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862920</v>
+        <v>862880</v>
       </c>
       <c r="R9" t="n">
-        <v>7312279</v>
+        <v>7312302</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916293</v>
+        <v>118916281</v>
       </c>
       <c r="B10" t="n">
-        <v>97766</v>
+        <v>79600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1499,19 +1495,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862911</v>
+        <v>862909</v>
       </c>
       <c r="R10" t="n">
-        <v>7312281</v>
+        <v>7312283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916252</v>
+        <v>118916264</v>
       </c>
       <c r="B11" t="n">
-        <v>97750</v>
+        <v>97880</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862850</v>
+        <v>862723</v>
       </c>
       <c r="R11" t="n">
-        <v>7312314</v>
+        <v>7312315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916290</v>
+        <v>118916271</v>
       </c>
       <c r="B12" t="n">
-        <v>97867</v>
+        <v>79594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862805</v>
+        <v>862932</v>
       </c>
       <c r="R12" t="n">
-        <v>7312360</v>
+        <v>7312260</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916259</v>
+        <v>118916257</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862773</v>
+        <v>862918</v>
       </c>
       <c r="R13" t="n">
-        <v>7312375</v>
+        <v>7312369</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916255</v>
+        <v>118916275</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1899,25 +1899,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862902</v>
+        <v>862906</v>
       </c>
       <c r="R14" t="n">
-        <v>7312092</v>
+        <v>7312275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1971,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1989,7 +1990,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916256</v>
+        <v>118916293</v>
       </c>
       <c r="B15" t="n">
         <v>97766</v>
@@ -2025,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862872</v>
+        <v>862911</v>
       </c>
       <c r="R15" t="n">
-        <v>7312079</v>
+        <v>7312281</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916287</v>
+        <v>118916259</v>
       </c>
       <c r="B16" t="n">
-        <v>97766</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2099,23 +2100,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2123,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862908</v>
+        <v>862773</v>
       </c>
       <c r="R16" t="n">
-        <v>7312314</v>
+        <v>7312375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916271</v>
+        <v>118916255</v>
       </c>
       <c r="B17" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2197,25 +2202,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>862932</v>
+        <v>862902</v>
       </c>
       <c r="R17" t="n">
-        <v>7312260</v>
+        <v>7312092</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2287,10 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916275</v>
+        <v>118916252</v>
       </c>
       <c r="B18" t="n">
-        <v>97867</v>
+        <v>97750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2303,21 +2308,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2327,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862906</v>
+        <v>862850</v>
       </c>
       <c r="R18" t="n">
-        <v>7312275</v>
+        <v>7312314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,7 +2376,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916285</v>
+        <v>118916245</v>
       </c>
       <c r="B19" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2402,25 +2406,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2430,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862926</v>
+        <v>862827</v>
       </c>
       <c r="R19" t="n">
-        <v>7312261</v>
+        <v>7312358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916248</v>
+        <v>118916290</v>
       </c>
       <c r="B20" t="n">
-        <v>57306</v>
+        <v>97867</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2504,25 +2508,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2532,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862924</v>
+        <v>862805</v>
       </c>
       <c r="R20" t="n">
-        <v>7312225</v>
+        <v>7312360</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,10 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916270</v>
+        <v>118916263</v>
       </c>
       <c r="B21" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2610,21 +2614,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862912</v>
+        <v>862841</v>
       </c>
       <c r="R21" t="n">
-        <v>7312266</v>
+        <v>7312301</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,10 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916264</v>
+        <v>118916272</v>
       </c>
       <c r="B22" t="n">
-        <v>97880</v>
+        <v>97766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2712,23 +2716,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>223597</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862723</v>
+        <v>862859</v>
       </c>
       <c r="R22" t="n">
-        <v>7312315</v>
+        <v>7312082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916277</v>
+        <v>118916285</v>
       </c>
       <c r="B23" t="n">
-        <v>57306</v>
+        <v>90504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2814,21 +2814,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>862845</v>
+        <v>862926</v>
       </c>
       <c r="R23" t="n">
-        <v>7312310</v>
+        <v>7312261</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916284</v>
+        <v>118916251</v>
       </c>
       <c r="B24" t="n">
-        <v>90504</v>
+        <v>79600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2912,25 +2912,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>862907</v>
+        <v>862918</v>
       </c>
       <c r="R24" t="n">
-        <v>7312315</v>
+        <v>7312229</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916262</v>
+        <v>118916277</v>
       </c>
       <c r="B25" t="n">
         <v>57306</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>862732</v>
+        <v>862845</v>
       </c>
       <c r="R25" t="n">
-        <v>7312367</v>
+        <v>7312310</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916289</v>
+        <v>118916288</v>
       </c>
       <c r="B26" t="n">
-        <v>79600</v>
+        <v>90504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3116,25 +3116,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>862932</v>
+        <v>862878</v>
       </c>
       <c r="R26" t="n">
-        <v>7312230</v>
+        <v>7312306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916276</v>
+        <v>118916260</v>
       </c>
       <c r="B27" t="n">
-        <v>79600</v>
+        <v>97867</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>862921</v>
+        <v>862772</v>
       </c>
       <c r="R27" t="n">
-        <v>7312277</v>
+        <v>7312370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916260</v>
+        <v>118916289</v>
       </c>
       <c r="B28" t="n">
-        <v>97867</v>
+        <v>79600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3324,21 +3324,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>862772</v>
+        <v>862932</v>
       </c>
       <c r="R28" t="n">
-        <v>7312370</v>
+        <v>7312230</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916272</v>
+        <v>118916283</v>
       </c>
       <c r="B29" t="n">
         <v>97766</v>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>862859</v>
+        <v>862846</v>
       </c>
       <c r="R29" t="n">
-        <v>7312082</v>
+        <v>7312100</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916263</v>
+        <v>118916276</v>
       </c>
       <c r="B30" t="n">
-        <v>57443</v>
+        <v>79600</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3520,25 +3520,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>862841</v>
+        <v>862921</v>
       </c>
       <c r="R30" t="n">
-        <v>7312301</v>
+        <v>7312277</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916251</v>
+        <v>118916269</v>
       </c>
       <c r="B31" t="n">
-        <v>79600</v>
+        <v>97766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3626,23 +3626,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3650,10 +3646,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>862918</v>
+        <v>862802</v>
       </c>
       <c r="R31" t="n">
-        <v>7312229</v>
+        <v>7312358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,10 +3708,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916245</v>
+        <v>118916262</v>
       </c>
       <c r="B32" t="n">
-        <v>97867</v>
+        <v>57306</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3724,25 +3720,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>862827</v>
+        <v>862732</v>
       </c>
       <c r="R32" t="n">
-        <v>7312358</v>
+        <v>7312367</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118916278</v>
+        <v>118916244</v>
       </c>
       <c r="B33" t="n">
-        <v>79600</v>
+        <v>79594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3830,21 +3826,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3854,10 +3850,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>862932</v>
+        <v>862920</v>
       </c>
       <c r="R33" t="n">
-        <v>7312260</v>
+        <v>7312279</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3912,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916257</v>
+        <v>118916270</v>
       </c>
       <c r="B34" t="n">
         <v>57306</v>
@@ -3956,10 +3952,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>862918</v>
+        <v>862912</v>
       </c>
       <c r="R34" t="n">
-        <v>7312369</v>
+        <v>7312266</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,10 +4014,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916269</v>
+        <v>118916279</v>
       </c>
       <c r="B35" t="n">
-        <v>97766</v>
+        <v>79565</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4030,23 +4026,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>862802</v>
+        <v>862909</v>
       </c>
       <c r="R35" t="n">
-        <v>7312358</v>
+        <v>7312283</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 22458-2024 artfynd.xlsx
+++ b/artfynd/A 22458-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916278</v>
+        <v>118916264</v>
       </c>
       <c r="B2" t="n">
-        <v>79600</v>
+        <v>97887</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862932</v>
+        <v>862723</v>
       </c>
       <c r="R2" t="n">
-        <v>7312260</v>
+        <v>7312315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916256</v>
+        <v>118916275</v>
       </c>
       <c r="B3" t="n">
-        <v>97766</v>
+        <v>97874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,19 +793,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862872</v>
+        <v>862906</v>
       </c>
       <c r="R3" t="n">
-        <v>7312079</v>
+        <v>7312275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -875,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916246</v>
+        <v>118916289</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,25 +892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862723</v>
+        <v>862932</v>
       </c>
       <c r="R4" t="n">
-        <v>7312315</v>
+        <v>7312230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118916292</v>
+        <v>118916277</v>
       </c>
       <c r="B5" t="n">
-        <v>90518</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862918</v>
+        <v>862845</v>
       </c>
       <c r="R5" t="n">
-        <v>7312342</v>
+        <v>7312310</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916287</v>
+        <v>118916252</v>
       </c>
       <c r="B6" t="n">
-        <v>97766</v>
+        <v>97757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,19 +1100,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1115,7 +1124,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862908</v>
+        <v>862850</v>
       </c>
       <c r="R6" t="n">
         <v>7312314</v>
@@ -1177,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916248</v>
+        <v>118916292</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>90525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1193,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862924</v>
+        <v>862918</v>
       </c>
       <c r="R7" t="n">
-        <v>7312225</v>
+        <v>7312342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118916284</v>
+        <v>118916272</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>97773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1291,27 +1300,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862907</v>
+        <v>862859</v>
       </c>
       <c r="R8" t="n">
-        <v>7312315</v>
+        <v>7312082</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118916273</v>
+        <v>118916271</v>
       </c>
       <c r="B9" t="n">
-        <v>97766</v>
+        <v>79601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,19 +1402,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1417,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862880</v>
+        <v>862932</v>
       </c>
       <c r="R9" t="n">
-        <v>7312302</v>
+        <v>7312260</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916281</v>
+        <v>118916269</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>97773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1495,23 +1504,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1519,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862909</v>
+        <v>862802</v>
       </c>
       <c r="R10" t="n">
-        <v>7312283</v>
+        <v>7312358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916264</v>
+        <v>118916281</v>
       </c>
       <c r="B11" t="n">
-        <v>97880</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1597,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862723</v>
+        <v>862909</v>
       </c>
       <c r="R11" t="n">
-        <v>7312315</v>
+        <v>7312283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916271</v>
+        <v>118916260</v>
       </c>
       <c r="B12" t="n">
-        <v>79594</v>
+        <v>97874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1699,21 +1704,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862932</v>
+        <v>862772</v>
       </c>
       <c r="R12" t="n">
-        <v>7312260</v>
+        <v>7312370</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916257</v>
+        <v>118916256</v>
       </c>
       <c r="B13" t="n">
-        <v>57306</v>
+        <v>97773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1797,27 +1802,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1825,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862918</v>
+        <v>862872</v>
       </c>
       <c r="R13" t="n">
-        <v>7312369</v>
+        <v>7312079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916275</v>
+        <v>118916257</v>
       </c>
       <c r="B14" t="n">
-        <v>97867</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1899,25 +1900,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862906</v>
+        <v>862918</v>
       </c>
       <c r="R14" t="n">
-        <v>7312275</v>
+        <v>7312369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,7 +1972,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916293</v>
+        <v>118916245</v>
       </c>
       <c r="B15" t="n">
-        <v>97766</v>
+        <v>97874</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2006,19 +2006,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862911</v>
+        <v>862827</v>
       </c>
       <c r="R15" t="n">
-        <v>7312281</v>
+        <v>7312358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916259</v>
+        <v>118916284</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2100,25 +2104,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862773</v>
+        <v>862907</v>
       </c>
       <c r="R16" t="n">
-        <v>7312375</v>
+        <v>7312315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916255</v>
+        <v>118916293</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>97773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2202,27 +2206,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>862902</v>
+        <v>862911</v>
       </c>
       <c r="R17" t="n">
-        <v>7312092</v>
+        <v>7312281</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916252</v>
+        <v>118916251</v>
       </c>
       <c r="B18" t="n">
-        <v>97750</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2308,21 +2308,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862850</v>
+        <v>862918</v>
       </c>
       <c r="R18" t="n">
-        <v>7312314</v>
+        <v>7312229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916245</v>
+        <v>118916263</v>
       </c>
       <c r="B19" t="n">
-        <v>97867</v>
+        <v>57443</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2406,25 +2406,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862827</v>
+        <v>862841</v>
       </c>
       <c r="R19" t="n">
-        <v>7312358</v>
+        <v>7312301</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916290</v>
+        <v>118916283</v>
       </c>
       <c r="B20" t="n">
-        <v>97867</v>
+        <v>97773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2512,23 +2512,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2536,10 +2532,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862805</v>
+        <v>862846</v>
       </c>
       <c r="R20" t="n">
-        <v>7312360</v>
+        <v>7312100</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916263</v>
+        <v>118916285</v>
       </c>
       <c r="B21" t="n">
-        <v>57443</v>
+        <v>90511</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2614,21 +2610,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862841</v>
+        <v>862926</v>
       </c>
       <c r="R21" t="n">
-        <v>7312301</v>
+        <v>7312261</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,10 +2696,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916272</v>
+        <v>118916278</v>
       </c>
       <c r="B22" t="n">
-        <v>97766</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2716,19 +2712,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223597</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862859</v>
+        <v>862932</v>
       </c>
       <c r="R22" t="n">
-        <v>7312082</v>
+        <v>7312260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916285</v>
+        <v>118916246</v>
       </c>
       <c r="B23" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2810,25 +2810,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>862926</v>
+        <v>862723</v>
       </c>
       <c r="R23" t="n">
-        <v>7312261</v>
+        <v>7312315</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916251</v>
+        <v>118916290</v>
       </c>
       <c r="B24" t="n">
-        <v>79600</v>
+        <v>97874</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2916,21 +2916,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>862918</v>
+        <v>862805</v>
       </c>
       <c r="R24" t="n">
-        <v>7312229</v>
+        <v>7312360</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916277</v>
+        <v>118916279</v>
       </c>
       <c r="B25" t="n">
-        <v>57306</v>
+        <v>79572</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>862845</v>
+        <v>862909</v>
       </c>
       <c r="R25" t="n">
-        <v>7312310</v>
+        <v>7312283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916288</v>
+        <v>118916255</v>
       </c>
       <c r="B26" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3116,25 +3116,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>862878</v>
+        <v>862902</v>
       </c>
       <c r="R26" t="n">
-        <v>7312306</v>
+        <v>7312092</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916260</v>
+        <v>118916276</v>
       </c>
       <c r="B27" t="n">
-        <v>97867</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>862772</v>
+        <v>862921</v>
       </c>
       <c r="R27" t="n">
-        <v>7312370</v>
+        <v>7312277</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916289</v>
+        <v>118916248</v>
       </c>
       <c r="B28" t="n">
-        <v>79600</v>
+        <v>57306</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3320,25 +3320,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>862932</v>
+        <v>862924</v>
       </c>
       <c r="R28" t="n">
-        <v>7312230</v>
+        <v>7312225</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916283</v>
+        <v>118916288</v>
       </c>
       <c r="B29" t="n">
-        <v>97766</v>
+        <v>90511</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3422,23 +3422,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3446,10 +3450,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>862846</v>
+        <v>862878</v>
       </c>
       <c r="R29" t="n">
-        <v>7312100</v>
+        <v>7312306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3512,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916276</v>
+        <v>118916259</v>
       </c>
       <c r="B30" t="n">
-        <v>79600</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3520,25 +3524,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>862921</v>
+        <v>862773</v>
       </c>
       <c r="R30" t="n">
-        <v>7312277</v>
+        <v>7312375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3614,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916269</v>
+        <v>118916273</v>
       </c>
       <c r="B31" t="n">
-        <v>97766</v>
+        <v>97773</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3646,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>862802</v>
+        <v>862880</v>
       </c>
       <c r="R31" t="n">
-        <v>7312358</v>
+        <v>7312302</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916262</v>
+        <v>118916287</v>
       </c>
       <c r="B32" t="n">
-        <v>57306</v>
+        <v>97773</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3720,27 +3724,23 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>862732</v>
+        <v>862908</v>
       </c>
       <c r="R32" t="n">
-        <v>7312367</v>
+        <v>7312314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
         <v>118916244</v>
       </c>
       <c r="B33" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916279</v>
+        <v>118916262</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>57306</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4030,21 +4030,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>862909</v>
+        <v>862732</v>
       </c>
       <c r="R35" t="n">
-        <v>7312283</v>
+        <v>7312367</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 22458-2024 artfynd.xlsx
+++ b/artfynd/A 22458-2024 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916269</v>
+        <v>118916281</v>
       </c>
       <c r="B10" t="n">
-        <v>97773</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1504,19 +1504,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1524,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862802</v>
+        <v>862909</v>
       </c>
       <c r="R10" t="n">
-        <v>7312358</v>
+        <v>7312283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916281</v>
+        <v>118916269</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>97773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1602,23 +1606,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862909</v>
+        <v>862802</v>
       </c>
       <c r="R11" t="n">
-        <v>7312283</v>
+        <v>7312358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916263</v>
+        <v>118916285</v>
       </c>
       <c r="B19" t="n">
-        <v>57443</v>
+        <v>90511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862841</v>
+        <v>862926</v>
       </c>
       <c r="R19" t="n">
-        <v>7312301</v>
+        <v>7312261</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916283</v>
+        <v>118916278</v>
       </c>
       <c r="B20" t="n">
-        <v>97773</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2512,19 +2512,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223597</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2532,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862846</v>
+        <v>862932</v>
       </c>
       <c r="R20" t="n">
-        <v>7312100</v>
+        <v>7312260</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,10 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916285</v>
+        <v>118916263</v>
       </c>
       <c r="B21" t="n">
-        <v>90511</v>
+        <v>57443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2610,21 +2614,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862926</v>
+        <v>862841</v>
       </c>
       <c r="R21" t="n">
-        <v>7312261</v>
+        <v>7312301</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,10 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916278</v>
+        <v>118916283</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>97773</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2712,23 +2716,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862932</v>
+        <v>862846</v>
       </c>
       <c r="R22" t="n">
-        <v>7312260</v>
+        <v>7312100</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 22458-2024 artfynd.xlsx
+++ b/artfynd/A 22458-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916264</v>
+        <v>118916251</v>
       </c>
       <c r="B2" t="n">
-        <v>97887</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862723</v>
+        <v>862918</v>
       </c>
       <c r="R2" t="n">
-        <v>7312315</v>
+        <v>7312229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916275</v>
+        <v>118916284</v>
       </c>
       <c r="B3" t="n">
-        <v>97874</v>
+        <v>90511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862906</v>
+        <v>862907</v>
       </c>
       <c r="R3" t="n">
-        <v>7312275</v>
+        <v>7312315</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916289</v>
+        <v>118916275</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>97874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862932</v>
+        <v>862906</v>
       </c>
       <c r="R4" t="n">
-        <v>7312230</v>
+        <v>7312275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118916277</v>
+        <v>118916246</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,25 +994,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862845</v>
+        <v>862723</v>
       </c>
       <c r="R5" t="n">
-        <v>7312310</v>
+        <v>7312315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916252</v>
+        <v>118916264</v>
       </c>
       <c r="B6" t="n">
-        <v>97757</v>
+        <v>97887</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862850</v>
+        <v>862723</v>
       </c>
       <c r="R6" t="n">
-        <v>7312314</v>
+        <v>7312315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916292</v>
+        <v>118916256</v>
       </c>
       <c r="B7" t="n">
-        <v>90525</v>
+        <v>97773</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,27 +1198,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1226,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862918</v>
+        <v>862872</v>
       </c>
       <c r="R7" t="n">
-        <v>7312342</v>
+        <v>7312079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118916272</v>
+        <v>118916262</v>
       </c>
       <c r="B8" t="n">
-        <v>97773</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,23 +1296,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862859</v>
+        <v>862732</v>
       </c>
       <c r="R8" t="n">
-        <v>7312082</v>
+        <v>7312367</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118916271</v>
+        <v>118916245</v>
       </c>
       <c r="B9" t="n">
-        <v>79601</v>
+        <v>97874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862932</v>
+        <v>862827</v>
       </c>
       <c r="R9" t="n">
-        <v>7312260</v>
+        <v>7312358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916281</v>
+        <v>118916244</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1504,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862909</v>
+        <v>862920</v>
       </c>
       <c r="R10" t="n">
-        <v>7312283</v>
+        <v>7312279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916269</v>
+        <v>118916276</v>
       </c>
       <c r="B11" t="n">
-        <v>97773</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,19 +1606,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1626,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862802</v>
+        <v>862921</v>
       </c>
       <c r="R11" t="n">
-        <v>7312358</v>
+        <v>7312277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916260</v>
+        <v>118916288</v>
       </c>
       <c r="B12" t="n">
-        <v>97874</v>
+        <v>90511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1700,25 +1704,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1728,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862772</v>
+        <v>862878</v>
       </c>
       <c r="R12" t="n">
-        <v>7312370</v>
+        <v>7312306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,10 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916256</v>
+        <v>118916263</v>
       </c>
       <c r="B13" t="n">
-        <v>97773</v>
+        <v>57443</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1802,23 +1806,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1826,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862872</v>
+        <v>862841</v>
       </c>
       <c r="R13" t="n">
-        <v>7312079</v>
+        <v>7312301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,7 +1896,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916257</v>
+        <v>118916277</v>
       </c>
       <c r="B14" t="n">
         <v>57306</v>
@@ -1928,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862918</v>
+        <v>862845</v>
       </c>
       <c r="R14" t="n">
-        <v>7312369</v>
+        <v>7312310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916245</v>
+        <v>118916292</v>
       </c>
       <c r="B15" t="n">
-        <v>97874</v>
+        <v>90525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2002,25 +2010,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2030,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862827</v>
+        <v>862918</v>
       </c>
       <c r="R15" t="n">
-        <v>7312358</v>
+        <v>7312342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,10 +2100,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916284</v>
+        <v>118916290</v>
       </c>
       <c r="B16" t="n">
-        <v>90511</v>
+        <v>97874</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2104,25 +2112,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862907</v>
+        <v>862805</v>
       </c>
       <c r="R16" t="n">
-        <v>7312315</v>
+        <v>7312360</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,7 +2202,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916293</v>
+        <v>118916287</v>
       </c>
       <c r="B17" t="n">
         <v>97773</v>
@@ -2230,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>862911</v>
+        <v>862908</v>
       </c>
       <c r="R17" t="n">
-        <v>7312281</v>
+        <v>7312314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916251</v>
+        <v>118916272</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>97773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2308,23 +2316,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2332,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862918</v>
+        <v>862859</v>
       </c>
       <c r="R18" t="n">
-        <v>7312229</v>
+        <v>7312082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,10 +2398,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916285</v>
+        <v>118916257</v>
       </c>
       <c r="B19" t="n">
-        <v>90511</v>
+        <v>57306</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2410,21 +2414,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2438,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862926</v>
+        <v>862918</v>
       </c>
       <c r="R19" t="n">
-        <v>7312261</v>
+        <v>7312369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,10 +2500,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916278</v>
+        <v>118916270</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>57306</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2508,25 +2512,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862932</v>
+        <v>862912</v>
       </c>
       <c r="R20" t="n">
-        <v>7312260</v>
+        <v>7312266</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,10 +2602,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916263</v>
+        <v>118916259</v>
       </c>
       <c r="B21" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2610,25 +2614,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862841</v>
+        <v>862773</v>
       </c>
       <c r="R21" t="n">
-        <v>7312301</v>
+        <v>7312375</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916283</v>
+        <v>118916248</v>
       </c>
       <c r="B22" t="n">
-        <v>97773</v>
+        <v>57306</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2712,23 +2716,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2736,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862846</v>
+        <v>862924</v>
       </c>
       <c r="R22" t="n">
-        <v>7312100</v>
+        <v>7312225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2798,10 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916246</v>
+        <v>118916293</v>
       </c>
       <c r="B23" t="n">
-        <v>97853</v>
+        <v>97773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2810,27 +2818,23 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2838,10 +2842,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>862723</v>
+        <v>862911</v>
       </c>
       <c r="R23" t="n">
-        <v>7312315</v>
+        <v>7312281</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,10 +2904,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916290</v>
+        <v>118916278</v>
       </c>
       <c r="B24" t="n">
-        <v>97874</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2916,21 +2920,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2940,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>862805</v>
+        <v>862932</v>
       </c>
       <c r="R24" t="n">
-        <v>7312360</v>
+        <v>7312260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916279</v>
+        <v>118916271</v>
       </c>
       <c r="B25" t="n">
-        <v>79572</v>
+        <v>79601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3014,25 +3018,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3042,10 +3046,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>862909</v>
+        <v>862932</v>
       </c>
       <c r="R25" t="n">
-        <v>7312283</v>
+        <v>7312260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916255</v>
+        <v>118916281</v>
       </c>
       <c r="B26" t="n">
-        <v>97853</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3116,25 +3120,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3144,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>862902</v>
+        <v>862909</v>
       </c>
       <c r="R26" t="n">
-        <v>7312092</v>
+        <v>7312283</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3206,10 +3210,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916276</v>
+        <v>118916269</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>97773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3222,23 +3226,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>223597</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>862921</v>
+        <v>862802</v>
       </c>
       <c r="R27" t="n">
-        <v>7312277</v>
+        <v>7312358</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916248</v>
+        <v>118916289</v>
       </c>
       <c r="B28" t="n">
-        <v>57306</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3320,25 +3320,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>862924</v>
+        <v>862932</v>
       </c>
       <c r="R28" t="n">
-        <v>7312225</v>
+        <v>7312230</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916288</v>
+        <v>118916252</v>
       </c>
       <c r="B29" t="n">
-        <v>90511</v>
+        <v>97757</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3422,25 +3422,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>862878</v>
+        <v>862850</v>
       </c>
       <c r="R29" t="n">
-        <v>7312306</v>
+        <v>7312314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916259</v>
+        <v>118916260</v>
       </c>
       <c r="B30" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3524,25 +3524,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>862773</v>
+        <v>862772</v>
       </c>
       <c r="R30" t="n">
-        <v>7312375</v>
+        <v>7312370</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916273</v>
+        <v>118916279</v>
       </c>
       <c r="B31" t="n">
-        <v>97773</v>
+        <v>79572</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3626,23 +3626,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3650,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>862880</v>
+        <v>862909</v>
       </c>
       <c r="R31" t="n">
-        <v>7312302</v>
+        <v>7312283</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,7 +3716,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916287</v>
+        <v>118916283</v>
       </c>
       <c r="B32" t="n">
         <v>97773</v>
@@ -3748,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>862908</v>
+        <v>862846</v>
       </c>
       <c r="R32" t="n">
-        <v>7312314</v>
+        <v>7312100</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3814,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118916244</v>
+        <v>118916255</v>
       </c>
       <c r="B33" t="n">
-        <v>79601</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3822,25 +3826,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3850,10 +3854,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>862920</v>
+        <v>862902</v>
       </c>
       <c r="R33" t="n">
-        <v>7312279</v>
+        <v>7312092</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,10 +3916,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916270</v>
+        <v>118916285</v>
       </c>
       <c r="B34" t="n">
-        <v>57306</v>
+        <v>90511</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3928,21 +3932,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3952,10 +3956,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>862912</v>
+        <v>862926</v>
       </c>
       <c r="R34" t="n">
-        <v>7312266</v>
+        <v>7312261</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4014,10 +4018,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916262</v>
+        <v>118916273</v>
       </c>
       <c r="B35" t="n">
-        <v>57306</v>
+        <v>97773</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4026,27 +4030,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>862732</v>
+        <v>862880</v>
       </c>
       <c r="R35" t="n">
-        <v>7312367</v>
+        <v>7312302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4113,6 +4113,210 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118916295</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97855</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rånön Bodön, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>862773</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7312369</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118916294</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97855</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rånön Bodön, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>862800</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7312367</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
